--- a/Lab2/Results_lab2_p1.xlsx
+++ b/Lab2/Results_lab2_p1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\chern\python\MPiAA\Lab2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{77116A1D-2CA4-4651-86B2-79B6E85362C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F7B5C72-9F2D-42A3-A2E4-EC1B7EFDCD02}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -227,7 +227,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -250,44 +250,35 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="17" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="17" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="17" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="17" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -314,55 +305,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>678180</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>144780</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>476742</xdr:colOff>
-      <xdr:row>10</xdr:row>
-      <xdr:rowOff>188929</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="Рисунок 1">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7F89F38E-EAC1-A7B1-BF49-8555EB3F60ED}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="6499860" y="144780"/>
-          <a:ext cx="3524742" cy="2391109"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -657,7 +599,7 @@
       <c r="G1" s="2"/>
     </row>
     <row r="2" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="8" t="s">
+      <c r="A2" s="15" t="s">
         <v>7</v>
       </c>
       <c r="B2" s="4">
@@ -666,65 +608,65 @@
       <c r="C2" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="8" t="s">
+      <c r="D2" s="15" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="9"/>
+      <c r="A3" s="16"/>
       <c r="B3" s="4">
         <v>1000</v>
       </c>
       <c r="C3" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="9"/>
+      <c r="D3" s="16"/>
     </row>
     <row r="4" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="9"/>
+      <c r="A4" s="16"/>
       <c r="B4" s="4">
         <v>10000</v>
       </c>
       <c r="C4" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="D4" s="9"/>
+      <c r="D4" s="16"/>
     </row>
     <row r="5" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="9"/>
+      <c r="A5" s="16"/>
       <c r="B5" s="4">
         <v>100000</v>
       </c>
       <c r="C5" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="D5" s="9"/>
+      <c r="D5" s="16"/>
       <c r="F5" s="2"/>
       <c r="G5" s="2"/>
     </row>
     <row r="6" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="9"/>
-      <c r="B6" s="13">
+      <c r="A6" s="16"/>
+      <c r="B6" s="10">
         <v>1000000</v>
       </c>
-      <c r="C6" s="23" t="s">
+      <c r="C6" s="14" t="s">
         <v>12</v>
       </c>
-      <c r="D6" s="10"/>
+      <c r="D6" s="20"/>
       <c r="F6" s="2"/>
       <c r="G6" s="2"/>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A7" s="11"/>
-      <c r="B7" s="12"/>
+      <c r="A7" s="8"/>
+      <c r="B7" s="9"/>
       <c r="C7" s="7"/>
-      <c r="D7" s="19"/>
+      <c r="D7" s="13"/>
       <c r="E7" s="2"/>
       <c r="F7" s="2"/>
       <c r="G7" s="2"/>
     </row>
     <row r="8" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="24" t="s">
+      <c r="A8" s="21" t="s">
         <v>8</v>
       </c>
       <c r="B8" s="6">
@@ -733,7 +675,7 @@
       <c r="C8" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="D8" s="21" t="s">
+      <c r="D8" s="17" t="s">
         <v>5</v>
       </c>
       <c r="E8" s="2"/>
@@ -741,167 +683,165 @@
       <c r="G8" s="2"/>
     </row>
     <row r="9" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="25"/>
+      <c r="A9" s="22"/>
       <c r="B9" s="4">
         <v>1000</v>
       </c>
       <c r="C9" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="D9" s="22"/>
+      <c r="D9" s="18"/>
       <c r="E9" s="2"/>
       <c r="F9" s="2"/>
       <c r="G9" s="2"/>
     </row>
     <row r="10" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="25"/>
+      <c r="A10" s="22"/>
       <c r="B10" s="4">
         <v>10000</v>
       </c>
       <c r="C10" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="D10" s="22"/>
+      <c r="D10" s="18"/>
       <c r="E10" s="2"/>
       <c r="F10" s="2"/>
       <c r="G10" s="2"/>
     </row>
     <row r="11" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="25"/>
+      <c r="A11" s="22"/>
       <c r="B11" s="4">
         <v>100000</v>
       </c>
       <c r="C11" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="D11" s="22"/>
+      <c r="D11" s="18"/>
       <c r="E11" s="2"/>
       <c r="F11" s="2"/>
       <c r="G11" s="2"/>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A12" s="26"/>
+      <c r="A12" s="23"/>
       <c r="B12" s="5">
         <v>1000000</v>
       </c>
       <c r="C12" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="D12" s="20"/>
+      <c r="D12" s="19"/>
       <c r="E12" s="2"/>
       <c r="F12" s="2"/>
       <c r="G12" s="2"/>
     </row>
     <row r="13" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="14"/>
-      <c r="B13" s="15"/>
-      <c r="C13" s="15"/>
-      <c r="D13" s="14"/>
+      <c r="A13" s="1"/>
+      <c r="B13" s="2"/>
+      <c r="C13" s="2"/>
+      <c r="D13" s="1"/>
       <c r="E13" s="2"/>
       <c r="F13" s="2"/>
       <c r="G13" s="2"/>
     </row>
     <row r="14" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="14"/>
-      <c r="B14" s="15"/>
-      <c r="C14" s="16"/>
-      <c r="D14" s="14"/>
+      <c r="A14" s="1"/>
+      <c r="B14" s="2"/>
+      <c r="C14" s="11"/>
+      <c r="D14" s="1"/>
       <c r="E14" s="2"/>
       <c r="F14" s="2"/>
       <c r="G14" s="2"/>
     </row>
     <row r="15" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="14"/>
-      <c r="B15" s="15"/>
-      <c r="C15" s="15"/>
-      <c r="D15" s="14"/>
+      <c r="A15" s="1"/>
+      <c r="B15" s="2"/>
+      <c r="C15" s="2"/>
+      <c r="D15" s="1"/>
       <c r="E15" s="2"/>
       <c r="F15" s="2"/>
       <c r="G15" s="2"/>
     </row>
     <row r="16" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="14"/>
-      <c r="B16" s="15"/>
-      <c r="C16" s="15"/>
-      <c r="D16" s="14"/>
+      <c r="A16" s="1"/>
+      <c r="B16" s="2"/>
+      <c r="C16" s="2"/>
+      <c r="D16" s="1"/>
       <c r="E16" s="2"/>
       <c r="F16" s="2"/>
       <c r="G16" s="2"/>
     </row>
     <row r="17" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="14"/>
-      <c r="B17" s="14"/>
-      <c r="C17" s="14"/>
-      <c r="D17" s="14"/>
+      <c r="A17" s="1"/>
+      <c r="B17" s="1"/>
+      <c r="C17" s="1"/>
+      <c r="D17" s="1"/>
       <c r="E17" s="2"/>
       <c r="F17" s="2"/>
       <c r="G17" s="2"/>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A18" s="14"/>
-      <c r="B18" s="15"/>
-      <c r="C18" s="15"/>
-      <c r="D18" s="14"/>
+      <c r="A18" s="1"/>
+      <c r="B18" s="2"/>
+      <c r="C18" s="2"/>
+      <c r="D18" s="1"/>
       <c r="F18" s="2"/>
       <c r="G18" s="2"/>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A19" s="14"/>
-      <c r="B19" s="15"/>
-      <c r="C19" s="15"/>
-      <c r="D19" s="14"/>
+      <c r="A19" s="1"/>
+      <c r="B19" s="2"/>
+      <c r="C19" s="2"/>
+      <c r="D19" s="1"/>
       <c r="F19" s="2"/>
       <c r="G19" s="2"/>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A20" s="14"/>
-      <c r="B20" s="15"/>
-      <c r="C20" s="15"/>
-      <c r="D20" s="14"/>
+      <c r="A20" s="1"/>
+      <c r="B20" s="2"/>
+      <c r="C20" s="2"/>
+      <c r="D20" s="1"/>
       <c r="F20" s="2"/>
       <c r="G20" s="2"/>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A21" s="14"/>
-      <c r="B21" s="15"/>
-      <c r="C21" s="15"/>
-      <c r="D21" s="14"/>
+      <c r="A21" s="1"/>
+      <c r="B21" s="2"/>
+      <c r="C21" s="2"/>
+      <c r="D21" s="1"/>
       <c r="E21" s="2"/>
       <c r="F21" s="2"/>
       <c r="G21" s="2"/>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A22" s="17"/>
-      <c r="B22" s="17"/>
-      <c r="C22" s="17"/>
-      <c r="D22" s="17"/>
+      <c r="A22" s="12"/>
+      <c r="B22" s="12"/>
+      <c r="C22" s="12"/>
+      <c r="D22" s="12"/>
       <c r="E22" s="2"/>
       <c r="F22" s="2"/>
       <c r="G22" s="2"/>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A23" s="14"/>
-      <c r="B23" s="15"/>
-      <c r="C23" s="18"/>
-      <c r="D23" s="14"/>
+      <c r="A23" s="1"/>
+      <c r="B23" s="2"/>
+      <c r="D23" s="1"/>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A24" s="14"/>
-      <c r="B24" s="15"/>
-      <c r="C24" s="16"/>
-      <c r="D24" s="14"/>
+      <c r="A24" s="1"/>
+      <c r="B24" s="2"/>
+      <c r="C24" s="11"/>
+      <c r="D24" s="1"/>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A25" s="14"/>
-      <c r="B25" s="15"/>
-      <c r="C25" s="18"/>
-      <c r="D25" s="14"/>
+      <c r="A25" s="1"/>
+      <c r="B25" s="2"/>
+      <c r="D25" s="1"/>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A26" s="14"/>
-      <c r="B26" s="15"/>
-      <c r="C26" s="16"/>
-      <c r="D26" s="14"/>
+      <c r="A26" s="1"/>
+      <c r="B26" s="2"/>
+      <c r="C26" s="11"/>
+      <c r="D26" s="1"/>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -911,6 +851,5 @@
     <mergeCell ref="A8:A12"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
 </worksheet>
 </file>
--- a/Lab2/Results_lab2_p1.xlsx
+++ b/Lab2/Results_lab2_p1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\chern\python\MPiAA\Lab2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F7B5C72-9F2D-42A3-A2E4-EC1B7EFDCD02}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C72475EB-036C-4831-945D-FB9A952186AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3384" yWindow="3336" windowWidth="17280" windowHeight="8880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="11">
   <si>
     <t>Время</t>
   </si>
@@ -39,12 +39,6 @@
     <t>0.015625</t>
   </si>
   <si>
-    <t>Сложность</t>
-  </si>
-  <si>
-    <t>O(n)</t>
-  </si>
-  <si>
     <t>Сортировка</t>
   </si>
   <si>
@@ -52,31 +46,6 @@
   </si>
   <si>
     <t>Стандартная сортировка</t>
-  </si>
-  <si>
-    <r>
-      <t>O(n</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="204"/>
-      </rPr>
-      <t>·log(n)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>)</t>
-    </r>
   </si>
   <si>
     <t>0.0625</t>
@@ -95,7 +64,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -110,13 +79,6 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <sz val="14"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <charset val="204"/>
-    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -126,7 +88,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="8">
+  <borders count="7">
     <border>
       <left/>
       <right/>
@@ -210,24 +172,11 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -259,7 +208,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="17" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -267,18 +215,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -570,20 +506,19 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G26"/>
+  <dimension ref="A1:F26"/>
   <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="18" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="23.88671875" style="3" customWidth="1"/>
     <col min="2" max="2" width="12" style="3" customWidth="1"/>
     <col min="3" max="3" width="32.6640625" style="3" customWidth="1"/>
-    <col min="4" max="4" width="25.21875" style="3" customWidth="1"/>
-    <col min="5" max="5" width="17.88671875" style="3" customWidth="1"/>
-    <col min="6" max="16384" width="9.109375" style="3"/>
+    <col min="4" max="4" width="17.88671875" style="3" customWidth="1"/>
+    <col min="5" max="16384" width="9.109375" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1" s="5" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B1" s="4" t="s">
         <v>1</v>
@@ -591,16 +526,13 @@
       <c r="C1" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="D1" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="E1" s="1"/>
+      <c r="D1" s="1"/>
+      <c r="E1" s="2"/>
       <c r="F1" s="2"/>
-      <c r="G1" s="2"/>
-    </row>
-    <row r="2" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="15" t="s">
-        <v>7</v>
+    </row>
+    <row r="2" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="14" t="s">
+        <v>5</v>
       </c>
       <c r="B2" s="4">
         <v>100</v>
@@ -608,66 +540,58 @@
       <c r="C2" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="15" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="16"/>
+    </row>
+    <row r="3" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="15"/>
       <c r="B3" s="4">
         <v>1000</v>
       </c>
       <c r="C3" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="16"/>
-    </row>
-    <row r="4" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="16"/>
+    </row>
+    <row r="4" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="15"/>
       <c r="B4" s="4">
         <v>10000</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="D4" s="16"/>
-    </row>
-    <row r="5" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="16"/>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="15"/>
       <c r="B5" s="4">
         <v>100000</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="D5" s="16"/>
+        <v>8</v>
+      </c>
+      <c r="E5" s="2"/>
       <c r="F5" s="2"/>
-      <c r="G5" s="2"/>
-    </row>
-    <row r="6" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="16"/>
+    </row>
+    <row r="6" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="15"/>
       <c r="B6" s="10">
         <v>1000000</v>
       </c>
-      <c r="C6" s="14" t="s">
-        <v>12</v>
-      </c>
-      <c r="D6" s="20"/>
+      <c r="C6" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="E6" s="2"/>
       <c r="F6" s="2"/>
-      <c r="G6" s="2"/>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A7" s="8"/>
       <c r="B7" s="9"/>
       <c r="C7" s="7"/>
-      <c r="D7" s="13"/>
+      <c r="D7" s="2"/>
       <c r="E7" s="2"/>
       <c r="F7" s="2"/>
-      <c r="G7" s="2"/>
-    </row>
-    <row r="8" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="21" t="s">
-        <v>8</v>
+    </row>
+    <row r="8" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="16" t="s">
+        <v>6</v>
       </c>
       <c r="B8" s="6">
         <v>100</v>
@@ -675,179 +599,156 @@
       <c r="C8" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="D8" s="17" t="s">
-        <v>5</v>
-      </c>
+      <c r="D8" s="2"/>
       <c r="E8" s="2"/>
       <c r="F8" s="2"/>
-      <c r="G8" s="2"/>
-    </row>
-    <row r="9" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="22"/>
+    </row>
+    <row r="9" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A9" s="17"/>
       <c r="B9" s="4">
         <v>1000</v>
       </c>
       <c r="C9" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="D9" s="18"/>
+      <c r="D9" s="2"/>
       <c r="E9" s="2"/>
       <c r="F9" s="2"/>
-      <c r="G9" s="2"/>
-    </row>
-    <row r="10" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="22"/>
+    </row>
+    <row r="10" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A10" s="17"/>
       <c r="B10" s="4">
         <v>10000</v>
       </c>
       <c r="C10" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="D10" s="18"/>
+      <c r="D10" s="2"/>
       <c r="E10" s="2"/>
       <c r="F10" s="2"/>
-      <c r="G10" s="2"/>
-    </row>
-    <row r="11" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="22"/>
+    </row>
+    <row r="11" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A11" s="17"/>
       <c r="B11" s="4">
         <v>100000</v>
       </c>
       <c r="C11" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="D11" s="18"/>
+      <c r="D11" s="2"/>
       <c r="E11" s="2"/>
       <c r="F11" s="2"/>
-      <c r="G11" s="2"/>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A12" s="23"/>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A12" s="18"/>
       <c r="B12" s="5">
         <v>1000000</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="D12" s="19"/>
+        <v>10</v>
+      </c>
+      <c r="D12" s="2"/>
       <c r="E12" s="2"/>
       <c r="F12" s="2"/>
-      <c r="G12" s="2"/>
-    </row>
-    <row r="13" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+    </row>
+    <row r="13" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="1"/>
       <c r="B13" s="2"/>
       <c r="C13" s="2"/>
-      <c r="D13" s="1"/>
+      <c r="D13" s="2"/>
       <c r="E13" s="2"/>
       <c r="F13" s="2"/>
-      <c r="G13" s="2"/>
-    </row>
-    <row r="14" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+    </row>
+    <row r="14" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="1"/>
       <c r="B14" s="2"/>
       <c r="C14" s="11"/>
-      <c r="D14" s="1"/>
+      <c r="D14" s="2"/>
       <c r="E14" s="2"/>
       <c r="F14" s="2"/>
-      <c r="G14" s="2"/>
-    </row>
-    <row r="15" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+    </row>
+    <row r="15" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="1"/>
       <c r="B15" s="2"/>
       <c r="C15" s="2"/>
-      <c r="D15" s="1"/>
+      <c r="D15" s="2"/>
       <c r="E15" s="2"/>
       <c r="F15" s="2"/>
-      <c r="G15" s="2"/>
-    </row>
-    <row r="16" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+    </row>
+    <row r="16" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="1"/>
       <c r="B16" s="2"/>
       <c r="C16" s="2"/>
-      <c r="D16" s="1"/>
+      <c r="D16" s="2"/>
       <c r="E16" s="2"/>
       <c r="F16" s="2"/>
-      <c r="G16" s="2"/>
-    </row>
-    <row r="17" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+    </row>
+    <row r="17" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A17" s="1"/>
       <c r="B17" s="1"/>
       <c r="C17" s="1"/>
-      <c r="D17" s="1"/>
+      <c r="D17" s="2"/>
       <c r="E17" s="2"/>
       <c r="F17" s="2"/>
-      <c r="G17" s="2"/>
-    </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.35">
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A18" s="1"/>
       <c r="B18" s="2"/>
       <c r="C18" s="2"/>
-      <c r="D18" s="1"/>
+      <c r="E18" s="2"/>
       <c r="F18" s="2"/>
-      <c r="G18" s="2"/>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.35">
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A19" s="1"/>
       <c r="B19" s="2"/>
       <c r="C19" s="2"/>
-      <c r="D19" s="1"/>
+      <c r="E19" s="2"/>
       <c r="F19" s="2"/>
-      <c r="G19" s="2"/>
-    </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.35">
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A20" s="1"/>
       <c r="B20" s="2"/>
       <c r="C20" s="2"/>
-      <c r="D20" s="1"/>
+      <c r="E20" s="2"/>
       <c r="F20" s="2"/>
-      <c r="G20" s="2"/>
-    </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.35">
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A21" s="1"/>
       <c r="B21" s="2"/>
       <c r="C21" s="2"/>
-      <c r="D21" s="1"/>
+      <c r="D21" s="2"/>
       <c r="E21" s="2"/>
       <c r="F21" s="2"/>
-      <c r="G21" s="2"/>
-    </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.35">
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A22" s="12"/>
       <c r="B22" s="12"/>
       <c r="C22" s="12"/>
-      <c r="D22" s="12"/>
+      <c r="D22" s="2"/>
       <c r="E22" s="2"/>
       <c r="F22" s="2"/>
-      <c r="G22" s="2"/>
-    </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.35">
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A23" s="1"/>
       <c r="B23" s="2"/>
-      <c r="D23" s="1"/>
-    </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.35">
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A24" s="1"/>
       <c r="B24" s="2"/>
       <c r="C24" s="11"/>
-      <c r="D24" s="1"/>
-    </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.35">
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A25" s="1"/>
       <c r="B25" s="2"/>
-      <c r="D25" s="1"/>
-    </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.35">
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A26" s="1"/>
       <c r="B26" s="2"/>
       <c r="C26" s="11"/>
-      <c r="D26" s="1"/>
     </row>
   </sheetData>
-  <mergeCells count="4">
+  <mergeCells count="2">
     <mergeCell ref="A2:A6"/>
-    <mergeCell ref="D8:D12"/>
-    <mergeCell ref="D2:D6"/>
     <mergeCell ref="A8:A12"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
